--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_02_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_02_22_Cau.xlsx
@@ -647,7 +647,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hành động đòi hỏi kiến thức nghiệp vụ thuộc về worker chuyên trách.</t>
+          <t>Trách nhiệm chuẩn của một supervisor mỏng (thin supervisor) trong kiến trúc multi-agent: (a) Phân loại yêu cầu đầu vào; (b) Lựa chọn worker chuyên trách phù hợp; (d) Theo dõi tiến độ thực thi và xử lý leo thang (escalation); (e) Tổng hợp kết quả cuối cùng có đầy đủ dấu vết truy vết. Supervisor mỏng tuyệt đối không tự ý áp đặt chính sách chuyên ngành thay cho worker.</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bên gọi và worker phải kiểm thử được mà không cần đọc prompt nội bộ.</t>
+          <t>Hợp đồng giao việc (task contract) cho RetrievalWorker cần bao gồm: (a) Nhiệm vụ cụ thể và ngữ cảnh được giới hạn chặt chẽ; (b) Các ràng buộc về phiên bản tài liệu, đối tượng áp dụng; (c) Schema đầu ra có cấu trúc rõ ràng; (d) Ngữ nghĩa và quy ước xử lý khi gặp lỗi hoặc không tìm thấy kết quả. Không được chuyển toàn bộ lịch sử và bí mật người dùng.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi field phải có kiểu dữ liệu và ý nghĩa trong vòng đời xử lý.</t>
+          <t>Các trường dữ liệu hợp lệ cho state điều phối có kiểu dữ liệu (strongly typed orchestration state): (a) `task: str`; (b) `retrieved_chunks: list[Chunk]`; (c) `policy_result: PolicyResult | None`; (d) `status: enum`; (e) `final_answer: str | None`. Tuyệt đối không đưa vào trường chứa dump toàn bộ prompt thô không kiểm soát.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Prompt phải nói cả được làm gì và không được làm gì.</t>
+          <t>Một prompt ra quyết định tối thiểu cho supervisor cần: (a) Danh sách các worker kèm bản tóm tắt năng lực cốt lõi; (b) Cấu trúc schema đầu ra được phép trả về; (c) Ranh giới phủ định (negative boundaries: không tự tiện suy đoán trả lời); (d) Hướng dẫn cách xử lý khi đầu vào bị thiếu hoặc mơ hồ. Không đưa toàn bộ chi tiết chính sách nghiệp vụ vào supervisor.</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi: sai ở bước này có hậu quả gì, và máy có đủ thẩm quyền/bằng chứng không?</t>
+          <t>Các tình huống bắt buộc phải có bước con người kiểm tra/phê duyệt (Human-in-the-Loop): (a) Thao tác hoàn tiền (refund) vượt ngưỡng giá trị quy định; (b) Khi hai nguồn sự thật có thẩm quyền mâu thuẫn trực tiếp và không thể tự phân giải; (c) Yêu cầu cấp quyền có hậu quả lớn nhưng độ tin cậy của mô hình thấp. Các tác vụ đọc thông thường hay tính toán xác định không cần chặn người duyệt.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_02_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_02_22_Cau.xlsx
@@ -678,10 +678,29 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi câu lệnh trong prompt nên được phân loại là điều phối luồng hay xử lý nghiệp vụ.
-Phân tích theo nguyên lý thiết kế: Mỗi câu lệnh trong prompt nên được phân loại là điều phối luồng hay xử lý nghiệp vụ.</t>
+- [Đặc tả ranh giới sạch của Supervisor] (1.5 điểm): Định nghĩa Supervisor là bộ điều phối thuần túy, chỉ xuất JSON routing có cấu trúc.
+- [Chuyển bỏ việc tự trả lời] (1.0 điểm): Xóa bỏ chỉ thị tự trả lời, chuyển nhiệm vụ này cho Policy/Synthesis Worker.
+- [Chuyển bỏ quyền gọi API hoàn tiền] (1.5 điểm): Tước quyền gọi API hoàn tiền của Supervisor, chuyển sang RefundPaymentWorker độc lập có cổng kiểm soát bảo mật.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Viết lại ranh giới trách nhiệm của Supervisor (Rewritten Supervisor Boundary):
+Supervisor là Bộ điều phối dòng chảy trung lập (Pure Orchestration Controller). Trách nhiệm duy nhất của nó là: Tiếp nhận yêu cầu, phân loại ý định, lựa chọn worker phù hợp nhất trong danh sách đã cấp và theo dõi trạng thái hoàn thành của toàn trình.
+- **Hợp đồng Đầu ra của Supervisor (Chỉ trả JSON Điều phối)**:
+  ```json
+  {
+    "action": "ROUTE",
+    "target_worker": "RetrievalWorker" | "PolicyWorker" | "RefundPaymentWorker" | "SynthesisWorker",
+    "instruction_payload": {"task_summary": "..."}
+  }
+  ```
+2. Các phần BẮT BUỘC PHẢI CHUYỂN ĐI (Mandatory Responsibilities to Evict):
+- **Phần 1: Chuyển bỏ 'Tự trả lời nếu biết' sang `SynthesisWorker` hoặc `PolicyWorker`**:
+  Tuyệt đối xóa bỏ câu lệnh 'nếu biết thì tự trả lời' khỏi prompt của supervisor. Supervisor không giữ tri thức chính sách; mọi câu trả lời nghiệp vụ phải do `PolicyWorker` thẩm định và `SynthesisWorker` soạn thảo dựa trên tài liệu trích xuất.
+- **Phần 2: Chuyển bỏ quyền 'Gọi API hoàn tiền' sang một Worker chuyên biệt có Guardrail (`RefundPaymentWorker`)**:
+  Supervisor không được nắm giữ tool thanh toán tài chính (vi phạm Least Privilege). Quyền gọi API hoàn tiền phải được chuyển sang một `RefundPaymentWorker` độc lập, có cổng kiểm duyệt Human-in-the-loop hoặc xác thực hạn mức trước khi thực thi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc trao quyền gọi công cụ tác động tài chính và quyền tự trả lời cho Supervisor là lỗi kiến trúc nguy hiểm (Over-privileged Controller Anti-pattern). Ranh giới sạch (Clean Boundary) yêu cầu tách rời hoàn toàn quyền điều phối khỏi quyền thao tác dữ liệu nhạy cảm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Multi-Agent Architecture Guidelines &amp; NIST SP 800-53 Principle of Least Privilege</t>
         </is>
       </c>
     </row>
@@ -760,10 +779,29 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một worker phải chạy lại được chỉ từ đầu vào của lần gọi đó.
-Phân tích theo nguyên lý thiết kế: Một worker phải chạy lại được chỉ từ đầu vào của lần gọi đó.</t>
+- [Phân rã thành 3 worker hẹp độc lập] (1.5 điểm): Tách thành RetrievalWorker, SupportTicketWorker, và AnswerSynthesisWorker có input/output/test boundary rõ ràng.
+- [Chỉ rõ bộ nhớ đệm hội thoại không được ẩn] (1.5 điểm): Khẳng định cấm ẩn conversation cache bên trong worker; bắt buộc đưa lên Shared Graph State.
+- [Nguyên lý Worker phi trạng thái tái lập] (1.0 điểm): Nhấn mạnh nguyên lý worker phải chạy lại được chỉ từ input truyền vào lần gọi đó.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tách hoặc Viết lại `UniversalWorker` thành các Worker có Ranh giới có thể Kiểm thử (Narrow Workers Decomposition):
+`UniversalWorker` là một 'God-Worker' gộp quá nhiều quyền và giữ state ẩn. Cần phân rã thành 3 worker độc lập, hoàn toàn phi trạng thái (Stateless Function Workers):
+- **1. RetrievalWorker**:
+  + Đầu vào: `{query: str, filters: dict}`. Đầu ra: `{chunks: List[dict]}`.
+  + Kiểm thử: Đo Recall@K trên tập benchmark ngữ liệu độc lập.
+- **2. SupportTicketWorker**:
+  + Đầu vào: `{ticket_payload: dict, idempotency_key: str}`. Đầu ra: `{ticket_id: str, status: str}`.
+  + Kiểm thử: Mock API endpoint của hệ thống phiếu hỗ trợ, kiểm tra schema request/response.
+- **3. AnswerSynthesisWorker**:
+  + Đầu vào: `{query: str, context_chunks: List[dict], user_intent: str}`. Đầu ra: `{final_answer: str, citations: List[str]}`.
+  + Kiểm thử: Kiểm thử độ bám bằng chứng (Faithfulness) và format markdown.
+2. Trạng thái (State) nào TUYỆT ĐỐI KHÔNG ĐƯỢC ẨN trong Worker:
+- **Bộ nhớ đệm hội thoại (Conversation Cache / Message History)**: Tuyệt đối không được lưu ẩn trong biến cục bộ (`self.cache` hoặc bộ nhớ tiến trình của worker).
+- **Quy tắc**: Toàn bộ lịch sử hội thoại và ngữ cảnh phiên làm việc bắt buộc phải được đưa lên **Lược đồ Trạng thái Chung của Đồ thị (Global Graph State / Checkpointed State Store)**.
+- Căn cứ: Một worker phải là một hàm thuần túy hoặc hàm đơn định (Pure / Idempotent Function): có thể chạy lại chính xác chỉ từ các tham số đầu vào được truyền vào trong lượt gọi đó, không phụ thuộc vào trạng thái ẩn trong bộ nhớ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Worker Hẹp và Phi Trạng thái (Stateless Narrow Workers): Ẩn trạng thái hội thoại bên trong worker phá hủy hoàn toàn khả năng tái lập lỗi, làm vô hiệu hóa cơ chế phục hồi checkpoint (Resume) của LangGraph và gây ra xung đột dữ liệu khi worker được scale ngang (Horizontal Scaling).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Stateless Nodes and Checkpointer Architecture' &amp; Twelve-Factor App: Stateless Processes</t>
         </is>
       </c>
     </row>
@@ -845,10 +883,43 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hai dữ kiện nào chỉ caller có thể biết?
-Phân tích theo nguyên lý thiết kế: Hai dữ kiện nào chỉ caller có thể biết?</t>
+- [Chỉ rõ 2 dữ kiện chỉ caller biết] (1.0 điểm): Xác định đúng employee_type (thời vụ/chính thức) và target_year (chính sách 2023 hay 2025).
+- [Đặc tả Contract đầu vào/đầu ra nghiêm ngặt] (1.5 điểm): Thiết kế schema có kiểu dữ liệu, bắt buộc truyền 2 trường trên, cấm silent default.
+- [Thiết kế phản hồi MISSING_INPUT làm rõ] (1.5 điểm): Soạn thảo response chuẩn có status MISSING_INPUT, mảng missing_fields và câu hỏi làm rõ thân thiện.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Viết lại Contract sửa lỗi cho Worker (Strict Worker Input/Output Contract):
+Worker bị lỗi âm thầm chọn bản 2023 vì hợp đồng đầu vào quá lỏng lẻo. Cần định nghĩa lại schema với các trường bắt buộc và xác thực chặt chẽ (Pydantic Schema):
+```json
+{
+  "input_schema": {
+    "question": {"type": "string", "required": true},
+    "employee_type": {"type": "string", "enum": ["permanent", "seasonal", "contractor"], "required": true},
+    "target_year": {"type": "integer", "minimum": 2023, "required": true}
+  },
+  "output_schema": {
+    "status": "SUCCESS" | "MISSING_INPUT" | "POLICY_NOT_FOUND",
+    "data": {"leave_duration_days": "integer", "policy_version": "string"},
+    "missing_fields": ["string"],
+    "clarification_prompt": "string"
+  }
+}
+```
+2. Hai dữ kiện chỉ Người gọi (Caller / User Session) có thể biết:
+- **Dữ kiện 1: Loại hình nhân viên của người hỏi (`employee_type`)**: Là nhân viên chính thức hay nhân viên thời vụ (chỉ hồ sơ nhân sự của caller mới biết).
+- **Dữ kiện 2: Năm áp dụng hoặc Thời điểm phát sinh thai sản (`target_year` / `effective_date`)**: Người hỏi đang hỏi cho chế độ của năm 2023 hay chính sách mới 2025.
+3. Phản hồi chuẩn mực khi thiếu thông tin đầu vào (Response for Missing Input):
+Tuyệt đối cấm âm thầm tự chọn. Worker phải trả về phản hồi yêu cầu làm rõ (Clarification Response):
+```json
+{
+  "status": "MISSING_INPUT",
+  "missing_fields": ["employee_type", "target_year"],
+  "clarification_prompt": "Để cung cấp thời gian nghỉ thai sản chính xác, vui lòng cho biết bạn là nhân viên chính thức hay thời vụ, và bạn cần tra cứu chính sách năm 2023 hay 2025?"
+}
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Hợp đồng Tác tử: 'Cấm suy đoán âm thầm khi thiếu dữ kiện nghiệp vụ' (Silent Defaulting Anti-pattern). Khi các tham số phân định chính sách thuộc về ngữ cảnh của người gọi, worker phải trả về trạng thái MISSING_INPUT kèm câu hỏi làm rõ có cấu trúc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Tool Use Specifications &amp; Pydantic / OpenAPI Schema Validation Standards</t>
         </is>
       </c>
     </row>
@@ -970,10 +1041,26 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt dữ kiện quyết định quy tắc với dữ kiện chỉ tình cờ có sẵn.
-Phân tích theo nguyên lý thiết kế: Phân biệt dữ kiện quyết định quy tắc với dữ kiện chỉ tình cờ có sẵn.</t>
+- [Chọn đúng 3 trường dữ liệu tối thiểu] (1.0 điểm): Giữ lại policy_result, employee_type, request_date.
+- [Biện minh chi tiết loại bỏ 3 trường nhạy cảm] (1.5 điểm): Giải thích rõ: loại bỏ chat history chống loãng context, loại bỏ địa chỉ bảo vệ PII, loại bỏ token chống rò rỉ quyền.
+- [Quy trình xử lý thiếu request_date] (1.5 điểm): Đưa ra cách xử lý: báo lỗi từ chối rõ ràng hoặc gán ngày hiện tại có kèm cờ cảnh báo kiểm toán.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Ngữ cảnh Tối thiểu cần gửi (Context Minimization Selection):
+Áp dụng Nguyên tắc Tối thiểu hóa Ngữ cảnh (Principle of Least Context / Data Minimization): Chỉ gửi chính xác **3 trường dữ liệu** cần thiết cho việc thẩm định quy tắc:
+- `policy_result`: Bắt buộc. Chứa các điều khoản quy định đã trích xuất từ văn bản chính sách để đối chiếu.
+- `employee_type`: Bắt buộc. Phân loại loại hình lao động của nhân viên để áp đúng khung điều kiện trong chính sách.
+- `request_date`: Bắt buộc. Ngày nộp đơn/yêu cầu để xác định phiên bản chính sách có hiệu lực và tính toán số ngày thâm niên.
+2. Giải thích vì sao BỎ RƠI toàn bộ hội thoại, địa chỉ nhà và access token:
+- **Toàn bộ lịch sử hội thoại (Full Chat History)**: Bỏ qua vì làm ô nhiễm context window bằng các câu chào hỏi râu ria, tốn token vô ích và làm xao nhãng mô hình.
+- **Địa chỉ nhà (Home Address - PII)**: Bỏ qua vì hoàn toàn không liên quan đến điều kiện hưởng chính sách, vi phạm nghiêm trọng quy chuẩn bảo vệ dữ liệu cá nhân (GDPR/Nghị định 13) nếu truyền tùy tiện giữa các worker.
+- **Access Token**: Bỏ qua vì PolicyWorker là một hàm suy luận logic thuần túy, không có quyền gọi dịch vụ ngoài. Việc truyền token vi phạm bảo mật nghiêm trọng (Credential Leakage Vulnerability).
+3. Cách xử lý nếu khuyết thiếu `request_date` (Handling Missing Request Date):
+- Kiểm tra hợp đồng đầu vào (Pre-condition Assertion): Nếu thiếu `request_date`, PolicyWorker từ chối xử lý và trả về mã lỗi: `{"status": "ERROR", "code": "MISSING_REQUEST_DATE", "message": "request_date is required to determine policy temporal validity"}`.
+- Phương án dự phòng có kiểm soát (Defaulting with Audit Flag): Nếu nghiệp vụ cho phép, Supervisor có thể điền mặc định bằng `current_system_date()` nhưng bắt buộc phải gắn cờ cảnh báo: `"date_inferred": true` trong payload.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống Multi-Agent, việc truyền bừa bãi toàn bộ đối tượng trạng thái (State Dump) chứa PII và Access Token giữa các node là một lỗ hổng an ninh thông tin nghiêm trọng. Mỗi tác tử chỉ được nhận đúng tập dữ liệu tối thiểu cần thiết để hoàn thành nhiệm vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLM: LLM06 Sensitive Information Disclosure &amp; Google Cloud Data Minimization Guide</t>
         </is>
       </c>
     </row>
@@ -1055,10 +1142,45 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách artifact theo ý nghĩa, rồi gán node sở hữu cho từng chuyển trạng thái.
-Phân tích theo nguyên lý thiết kế: Tách artifact theo ý nghĩa, rồi gán node sở hữu cho từng chuyển trạng thái.</t>
+- [Đặc tả Typed State Schema chi tiết] (2.0 điểm): Định nghĩa schema có kiểu dữ liệu rõ ràng, tách riêng user_query, retrieved_policies, eligibility_decision, final_answer.
+- [Phân định quyền Đọc/Ghi cho từng Node] (1.5 điểm): Chỉ rõ quyền đọc/ghi độc quyền của từng node qua từng bước chuyển trạng thái.
+- [Khắc phục lỗi mất policy result khi resume] (0.5 điểm): Khẳng định việc tách trường độc quyền giúp checkpoint lưu giữ nguyên vẹn kết quả khi chạy lại.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế lại Lược đồ Trạng thái Chung có Kiểu dữ liệu Chặt chẽ (Typed Graph State Schema):
+Thay thế schema lỏng lẻo `{messages, data, done}` bằng TypedDict / Pydantic schema phân rã các artifact ngữ nghĩa rõ ràng:
+```python
+from typing import Annotated, List, Optional, TypedDict
+from langgraph.graph.message import add_messages
+class PolicyChunk(TypedDict):
+    chunk_id: str
+    content: str
+    policy_version: str
+class SharedGraphState(TypedDict):
+    messages: Annotated[List[dict], add_messages]      # Lịch sử hội thoại
+    user_query: str                                     # Câu hỏi gốc của người dùng
+    employee_context: Optional[dict]                    # Dữ liệu nhân viên từ CRM
+    retrieved_policies: Optional[List[PolicyChunk]]     # Artifact chính sách trích xuất
+    eligibility_decision: Optional[dict]                # Phán quyết điều kiện đủ
+    final_answer: Optional[str]                         # Câu trả lời cuối cùng
+    current_step: str                                   # Bước điều phối hiện tại
+    is_completed: bool                                  # Cờ kết thúc hoàn tất
+```
+2. Phân định quyền Đọc/Ghi ở từng chuyển trạng thái (State Transition Permissions):
+- **Node 1: UserInputNode / Router**:
+  + Ghi: `user_query`, `current_step = 'routing'`.
+- **Node 2: RetrievalWorker**:
+  + Đọc: `user_query`.
+  + Ghi độc quyền: `retrieved_policies` (Bảo đảm artifact chính sách được ghi nhận độc lập, không bị mất khi resume).
+- **Node 3: PolicyWorker**:
+  + Đọc: `retrieved_policies`, `employee_context`.
+  + Ghi độc quyền: `eligibility_decision`.
+- **Node 4: SynthesisWorker**:
+  + Đọc: `retrieved_policies`, `eligibility_decision`.
+  + Ghi: `final_answer`, `is_completed = True`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc sử dụng một trường `data: any` cho mọi node ghi đè là nguồn gốc của các lỗi mất mát trạng thái khi hệ thống khôi phục sau sự cố (Resume failure). Một lược đồ trạng thái mạnh (Strongly-typed State Schema) phân rã từng artifact thành các thuộc tính riêng biệt và gán quyền sở hữu độc quyền cho từng bước chuyển trạng thái.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Defining State Schemas with TypedDict &amp; Pydantic' &amp; Checkpointing Architecture</t>
         </is>
       </c>
     </row>
@@ -1141,10 +1263,33 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi field cần một bên ghi và ngữ nghĩa gộp dữ liệu, nhất là khi thử lại.
-Phân tích theo nguyên lý thiết kế: Mỗi field cần một bên ghi và ngữ nghĩa gộp dữ liệu, nhất là khi thử lại.</t>
+- [Phân tích đúng 3 xung đột ghi đè] (1.0 điểm): Chỉ ra xung đột sources giữa 2 worker, supervisor ghi đè final_answer, và retry làm mất nguồn cũ.
+- [Quy tắc Single-Writer &amp; Tách trường sources] (1.5 điểm): Cấm supervisor ghi đè final_answer; tách sources thành retrieval_sources và policy_citations.
+- [Thiết kế Reducer gộp dữ liệu khi Retry] (1.5 điểm): Cung cấp logic reducer tích lũy và khử trùng lặp nguồn khi thử lại, bảo đảm không thất thoát dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích xung đột ghi đè âm thầm (Silent Overwrite Defect):
+- Xung đột 1 (`sources`): Cả RetrievalWorker và PolicyWorker đều ghi vào trường `sources`. Khi PolicyWorker chạy sau, nó ghi đè hoàn toàn danh sách nguồn của RetrievalWorker, làm mất các tài liệu tham khảo ban đầu.
+- Xung đột 2 (`final_answer`): Supervisor ghi đè câu trả lời đã được tra cứu kỹ của worker.
+- Xung đột 3 (Retry Loss): Khi thử lại (Retry), hệ thống khởi tạo lại mảng rỗng, làm xóa sạch các nguồn thành công ở lần thử trước.
+2. Thiết kế Quy tắc Sở hữu và Cơ chế Gộp dữ liệu (Ownership &amp; Reducer Rules):
+- **Quy tắc Sở hữu Đơn quyền (Single-Writer Ownership Principle)**:
+  + Trường `final_answer`: Chỉ DUY NHẤT một node có thẩm quyền ghi, đó là `SynthesisWorker`. Supervisor tuyệt đối cấm ghi đè vào trường này.
+  + Tách trường nguồn dữ liệu theo chủ quản: Tách `sources` thành hai trường phân biệt: `retrieval_sources: List[dict]` (do RetrievalWorker sở hữu) và `policy_rule_citations: List[dict]` (do PolicyWorker sở hữu).
+- **Ngữ nghĩa Gộp dữ liệu khi Thử lại (Additive / Append Reducer Semantics)**:
+  + Sử dụng hàm gộp Reducer (ví dụ `operator.add` hoặc hàm gộp khử trùng lặp có nhận biết retry) cho danh sách nguồn:
+    ```python
+    def merge_sources(existing: List[dict], new_items: List[dict]) -&gt; List[dict]:
+        # Gộp và khử trùng lặp theo source_id, giữ lại cả nguồn cũ và mới
+        combined = {item['source_id']: item for item in existing}
+        for item in new_items:
+            combined[item['source_id']] = item
+        return list(combined.values())
+    ```
+  + Khi có lần thử lại (Retry), các nguồn hợp lệ từ lần chạy trước không bị xóa mà được tích lũy bổ sung vào danh sách.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong lập trình điều phối tác tử phân tán, tài nguyên trạng thái chia sẻ (Shared State) phải được bảo vệ bằng các hàm Reducer xác định và nguyên tắc Đơn quyền sở hữu. Tránh ghi đè tùy tiện bằng cách quy định rõ node nào được phép cập nhật thuộc tính nào.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'State Reducers and Annotations' (https://langchain-ai.github.io/langgraph/concepts/low_level/#reducers)</t>
         </is>
       </c>
     </row>
@@ -1265,10 +1410,36 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Graph cần một tập lựa chọn quyết định hữu hạn và một nhánh kết thúc cho giá trị không biết.
-Phân tích theo nguyên lý thiết kế: Graph cần một tập lựa chọn quyết định hữu hạn và một nhánh kết thúc cho giá trị không biết.</t>
+- [Phê phán cách so khớp chuỗi con] (1.0 điểm): Chỉ ra rủi ro sai lệch của substring matching khi classifier trả văn xuôi dài.
+- [Đặc tả Schema với tập Enum hữu hạn] (1.5 điểm): Thiết kế schema JSON ràng buộc trường next_node thuộc tập Enum đóng có cấu trúc.
+- [Xử lý giá trị không biết &amp; Fallback branch] (1.5 điểm): Thiết lập cơ chế kiểm tra schema và định tuyến giá trị UNKNOWN về nhánh an toàn/làm rõ/con người.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phê phán cơ chế định tuyến hiện tại (Flaw of Substring Matching):
+Việc Classifier trả về các chuỗi tự do mập mờ (`next='maybe-tools'`, câu giải thích dài) và đồ thị dùng cách so khớp chuỗi con (`substring in output`) là một thiết kế lỏng lẻo, cực kỳ dễ vỡ (Brittle String Parsing): Một câu như 'Tôi không nghĩ nên gọi tools' vẫn chứa chuỗi con 'tools' và khiến đồ thị rẽ nhầm nhánh!
+2. Định nghĩa Schema Đầu ra Định tuyến Tường minh (Explicit Routing Schema Contract):
+Bắt buộc Classifier xuất ra đối tượng JSON theo một tập giá trị đóng hữu hạn (Finite Enum) qua Pydantic / Structured Outputs:
+```json
+{
+  "type": "object",
+  "properties": {
+    "next_node": {
+      "type": "string",
+      "enum": ["retrieval_node", "billing_tool_node", "direct_answer_node", "human_review_node", "UNKNOWN"]
+    },
+    "confidence_score": {"type": "number", "minimum": 0.0, "maximum": 1.0},
+    "decision_reason": {"type": "string"}
+  },
+  "required": ["next_node", "confidence_score"]
+}
+```
+3. Cơ chế Kiểm tra và Xử lý Giá trị Không biết (Validation &amp; Unknown Handling):
+- **Bộ kiểm tra hợp đồng (Schema Validator)**: Đọc đầu ra. Nếu không parse được JSON hoặc `next_node` không thuộc tập Enum cho phép, gán ngay `next_node = 'UNKNOWN'`.
+- **Nhánh kết thúc cho giá trị không biết (Safe Fallback / Dead-Letter Branch)**:
+  Đồ thị định tuyến: Nếu `next_node == 'UNKNOWN'` hoặc `confidence_score &lt; 0.60`, đồ thị lập tức rẽ nhánh an toàn sang `fallback_clarification_node` (Yêu cầu người dùng làm rõ câu hỏi) hoặc chuyển cấp sang `human_review_node`, tuyệt đối không tự ý chạy bừa một tool nào.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Tín hiệu định tuyến (Routing Signal) trong đồ thị tác tử phải là một tín hiệu số tất định (Deterministic Enum Signal). Tuyệt đối không được dựa dẫm vào việc bóc tách chuỗi văn xuôi tự do. Khái niệm 'Dead-Letter Branch' cho các tín hiệu lạ bảo đảm hệ thống luôn có lối thoát an toàn khi gặp tình huống bất định.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'Structured Outputs and Conditional Routing' &amp; Pydantic Enums</t>
         </is>
       </c>
     </row>
@@ -1350,10 +1521,37 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một đầu ra phải được bộ kiểm tra chấp nhận hoặc từ chối rõ ràng.
-Phân tích theo nguyên lý thiết kế: Một đầu ra phải được bộ kiểm tra chấp nhận hoặc từ chối rõ ràng.</t>
+- [Phê phán prompt mơ hồ hiện tại] (1.0 điểm): Nhận diện lỗi prompt thiếu ràng buộc khiến mô hình hành xử tùy tiện.
+- [Soạn thảo Prompt Contract đầy đủ] (1.5 điểm): Viết lại prompt có định nghĩa vai trò điều phối thuần túy, danh sách worker năng lực rõ ràng, và cấm tự trả lời.
+- [Đặc tả JSON Schema &amp; Cổng kiểm tra tự động] (1.5 điểm): Ràng buộc định dạng JSON chuẩn (next_worker, reason) và cơ chế validator chấp nhận/từ chối.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích nguyên nhân prompt hiện tại thất bại:
+Prompt `Bạn là supervisor thông minh. Hãy xử lý yêu cầu tốt nhất` là một prompt không có hợp đồng (Contract-less Prompt), quá mơ hồ và không định hình vai trò. Mô hình không biết khi nào cần điều phối và khi nào cần trả lời, dẫn đến hành vi ngẫu nhiên không tất định (lúc trả tên worker, lúc tự viết câu trả lời).
+2. Viết lại Prompt Contract Định tuyến Tất định (Rewritten Supervisor Prompt Contract):
+```markdown
+# VAI TRÒ:
+Bạn là Supervisor Điều phối Luồng Tác tử (Agent Flow Orchestrator). Bạn CHỈ CÓ NHIỆM VỤ ĐỊNH TUYẾN. Bạn TUYỆT ĐỐI KHÔNG ĐƯỢC tự viết câu trả lời cho người dùng.
+# DANH SÁCH WORKER CHO PHÉP VÀ NĂNG LỰC:
+1. `PolicyWorker`: Tra cứu và giải thích quy chế đào tạo, sổ tay sinh viên.
+2. `EnrollmentToolWorker`: Tra cứu số dư chỗ ngồi và đăng ký tín chỉ.
+3. `SynthesisWorker`: Soạn thảo câu trả lời khi tất cả dữ liệu đã được thu thập đầy đủ.
+4. `FINISH`: Kết thúc phiên làm việc.
+# QUY TẮC BẮT BUỘC:
+- Đầu ra của bạn BẮT BUỘC là một JSON object hợp lệ, TUYỆT ĐỐI KHÔNG thêm lời giải thích ngoài khối JSON.
+- Trường `next_worker` chỉ được chọn từ danh sách: ["PolicyWorker", "EnrollmentToolWorker", "SynthesisWorker", "FINISH"].
+# ĐỊNH DẠNG ĐẦU RA:
+{
+  "next_worker": "&lt;Tên worker duy nhất được chọn&gt;",
+  "reason": "&lt;Căn cứ ngắn gọn 1 câu giải thích vì sao chọn worker này&gt;",
+  "task_instruction": "&lt;Chỉ thị cụ thể chuyển tiếp cho worker&gt;"
+}
+```
+3. Kiểm soát chấp nhận hoặc từ chối (Acceptance / Rejection Gate):
+Hệ thống bọc lệnh gọi bằng bộ kiểm tra Pydantic: Nếu đầu ra không phải JSON hoặc `next_worker` nằm ngoài danh mục 4 từ khóa trên, lập tức từ chối và kích hoạt retry với thông báo lỗi cụ thể.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Prompt Engineering cho Tác tử Điều phối: Biến mô hình ngôn ngữ thành một máy trạng thái hữu hạn (Finite State Machine). Ràng buộc vai trò dứt khoát, giới hạn tập hành động cho phép và ép định dạng JSON là ba trụ cột bảo đảm tính tất định.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Prompt Engineering Guide: 'System Prompts and Structured Outputs' &amp; OpenAI Function Calling</t>
         </is>
       </c>
     </row>
@@ -1433,10 +1631,29 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Agent từ xa không phải một node có quyền đọc/ghi mọi field cục bộ.
-Phân tích theo nguyên lý thiết kế: Agent từ xa không phải một node có quyền đọc/ghi mọi field cục bộ.</t>
+- [Chọn đúng A2A Message Contract] (1.5 điểm): Chọn hợp đồng thông điệp có cấu trúc (JSON-RPC/REST), bác bỏ việc gửi LangGraph state cục bộ.
+- [Liệt kê các trường được truyền] (1.0 điểm): Xác định đúng task_id, query_statement, parameters sạch.
+- [Liệt kê các trường cấm truyền] (1.0 điểm): Cấm truyền biến LangGraph nội bộ, PII và auth tokens.
+- [Cơ chế parse response có cấu trúc] (0.5 điểm): Yêu cầu parse và validate schema response trước khi map vào state nội bộ, cấm nhận văn xuôi tùy tiện.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Hợp đồng Đúng cho Ranh giới Liên tác tử (Cross-Boundary Contract Selection):
+- Quyết định: **SỬ DỤNG HỢP ĐỒNG TIN NHẮN TÁC TỬ CÓ CẤU TRÚC (Structured Agent-to-Agent / A2A Message Contract)**, ví dụ JSON-RPC hoặc REST Task Contract. TUYỆT ĐỐI KHÔNG GỬI TOÀN BỘ LANGGRAPH STATE CỤC BỘ.
+- Lý do: Agent đối tác là một hệ thống bên ngoài ranh giới tin cậy (External Trust Boundary). Gửi toàn bộ LangGraph state cục bộ là lỗi rò rỉ ranh giới (Encapsulation Leak), vừa lộ toàn bộ cấu trúc biến nội bộ, vừa đối mặt rủi ro nhận lại văn xuôi tùy tiện làm sập đồ thị.
+2. Danh mục các Trường CẦN TRUYỀN (Required Outbound Fields):
+- `task_id`: Mã định danh nhiệm vụ duy nhất để theo dõi tương quan.
+- `query_statement`: Yêu cầu nghiệp vụ cụ thể cần đối tác thực hiện.
+- `parameters`: Tập tham số đầu vào được lọc sạch (chỉ chứa dữ liệu cần thiết cho tác vụ đó).
+- `callback_url` / `timeout_seconds`: Thông số kỹ thuật của cuộc gọi.
+3. Danh mục các Trường TUYỆT ĐỐI KHÔNG ĐƯỢC TRUYỀN (Forbidden Outbound Fields):
+- Toàn bộ biến nội bộ của LangGraph (`checkpoint_id`, `thread_id`, `node_history`, `internal_flags`).
+- Dữ liệu nhạy cảm của người dùng (PII, Auth tokens, session cookies).
+- Dữ liệu thô của các worker nội bộ khác không liên quan.
+4. Xử lý phản hồi từ đối tác:
+Phản hồi từ đối tác bắt buộc phải tuân thủ Schema kết quả: `{task_id, status: 'SUCCESS'|'ERROR', result_payload: dict}`. Phải có bộ Parser xác thực schema trước khi ánh xạ kết quả vào LangGraph state cục bộ, cấm gán nguyên văn xuôi vào state.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ranh giới giữa các tác tử thuộc các tổ chức/hệ thống khác nhau (Cross-Agent Trust Boundary) phải là ranh giới thông điệp lỏng lẻo (Loosely Coupled Message Protocol). Chia sẻ không gian bộ nhớ/state trực tiếp phá hủy tính bao gói và tạo ra các lỗ hổng bảo mật nghiêm trọng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic / Model Context Protocol: 'Trust Boundaries' &amp; Enterprise Integration Patterns: 'Message-Based Integration'</t>
         </is>
       </c>
     </row>
@@ -1518,10 +1735,39 @@
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Thiết kế cả lúc dừng lẫn cách tiếp tục an toàn.
-Phân tích theo nguyên lý thiết kế: Thiết kế cả lúc dừng lẫn cách tiếp tục an toàn.</t>
+- [Thiết kế State AWAITING_HUMAN_REVIEW] (1.0 điểm): Định nghĩa điều kiện kích hoạt: tiền &gt;= 1 triệu hoặc bằng chứng mâu thuẫn.
+- [Đặc tả Payload cho người duyệt đầy đủ] (1.5 điểm): Thiết kế JSON payload hiển thị cho admin: case_id, amount, trigger_reason, policy clause, citations.
+- [Thao tác Approve/Reject &amp; Cơ chế Resume an toàn] (1.5 điểm): Trình bày rõ ràng luồng resume từ checkpoint khi approve (gọi payment) và rẽ nhánh từ chối khi reject.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Trạng thái Chờ Kiểm tra (Interrupt / Paused State):
+Trong LangGraph, sử dụng cơ chế `interrupt_before=['execute_refund']` hoặc gắn nhãn trạng thái:
+- Trạng thái: `state.status = 'AWAITING_HUMAN_REVIEW'`.
+- Điều kiện kích hoạt rẽ nhánh vào trạng thái này:
+  `if refund_amount &gt;= 1_000_000 or policy_evidence.has_conflicts == True:`
+2. Thiết kế Payload Cung cấp cho Người duyệt (Reviewer Payload Contract):
+Payload gửi lên giao diện quản trị viên (Admin Review Dashboard) phải súc tích, đầy đủ bằng chứng để ra quyết định ngay lập tức:
+```json
+{
+  "case_id": "REF-2026-9981",
+  "user_id": "USR-4412",
+  "amount": 1500000,
+  "trigger_reason": "EXCEEDS_THRESHOLD_1M",
+  "evidence_summary": {
+    "policy_clause": "Điều 8.2: Hoàn phí đặc biệt khi có xác nhận y tế",
+    "conflict_flag": false,
+    "source_citations": ["policy_v3.pdf#page=12"]
+  },
+  "created_at": "2026-10-23T14:30:00Z"
+}
+```
+3. Thao tác Chấp thuận / Từ chối và Cách Tiếp tục Chạy an toàn (Resume Protocol):
+- Người vận hành nhấn nút trên UI gửi API request:
+  + **Nếu Chấp thuận (Approve)**: Gửi payload `{action: 'APPROVE', reviewer_id: 'AD-09', note: 'Đủ điều kiện y tế'}`. Hệ thống cập nhật `state.status = 'APPROVED'`, ghi nhật ký kiểm toán và kích hoạt lệnh tiếp tục chạy từ checkpoint: `graph.invoke(Command(resume={'approved': True}), config=thread_config)` để gọi `PaymentToolWorker`.
+  + **Nếu Từ chối (Reject)**: Gửi payload `{action: 'REJECT', reviewer_id: 'AD-09', reason: 'Thiếu bệnh án gốc'}`. Hệ thống cập nhật `state.status = 'REJECTED'`, chuyển thẳng sang node thông báo từ chối cho học viên, không gọi tool thanh toán.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Cơ chế Con người trong Vòng lặp (Human-in-the-Loop - HITL) là hàng rào phòng thủ tối thượng cho các hành động có rủi ro tài chính cao. Framework điều phối hiện đại (như LangGraph) sử dụng cơ chế Checkpointing và Resume Interrupt để đóng băng trạng thái an toàn, chờ phê duyệt có xác thực danh tính trước khi giải phóng tác dụng phụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Human-in-the-Loop &amp; Breakpoints' (https://langchain-ai.github.io/langgraph/how-tos/human-in-the-loop/)</t>
         </is>
       </c>
     </row>
